--- a/docs/ke-hoach/SWP391_UCP_Sprint_Role_Split.xlsx
+++ b/docs/ke-hoach/SWP391_UCP_Sprint_Role_Split.xlsx
@@ -942,7 +942,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
               </a:p>
             </txPr>
@@ -1074,7 +1074,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -1163,7 +1163,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -1447,7 +1447,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="47">
       <c r="A4" s="50" t="inlineStr">
         <is>
@@ -1792,7 +1791,6 @@
         </is>
       </c>
     </row>
-    <row r="38"/>
     <row r="39" ht="15" customHeight="1" s="47">
       <c r="A39" s="50" t="inlineStr">
         <is>
@@ -6303,7 +6301,7 @@
       </c>
       <c r="N60" s="66" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="O60" s="67" t="inlineStr">
@@ -6376,12 +6374,12 @@
       </c>
       <c r="N61" s="66" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="O61" s="67" t="inlineStr">
         <is>
-          <t>sprint-3/be-nhanh, sprint-3/fe-khai</t>
+          <t>sprint-3/be-nhanh (BE xong, chờ FE)</t>
         </is>
       </c>
     </row>
@@ -6449,12 +6447,12 @@
       </c>
       <c r="N62" s="66" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="O62" s="67" t="inlineStr">
         <is>
-          <t>sprint-3/be-nhanh, sprint-3/fe-khai</t>
+          <t>sprint-3/be-nhanh (BE xong, chờ FE)</t>
         </is>
       </c>
     </row>
@@ -6522,12 +6520,12 @@
       </c>
       <c r="N63" s="66" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="O63" s="67" t="inlineStr">
         <is>
-          <t>sprint-3/be-nhanh, sprint-3/fe-khoi</t>
+          <t>sprint-3/be-nhanh (BE xong, chờ FE)</t>
         </is>
       </c>
     </row>
@@ -8639,12 +8637,12 @@
       </c>
       <c r="N92" s="66" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="O92" s="67" t="inlineStr">
         <is>
-          <t>sprint-3/be-nhanh, sprint-3/fe-khai</t>
+          <t>sprint-3/be-nhanh (BE xong, chờ FE)</t>
         </is>
       </c>
     </row>
@@ -8712,12 +8710,12 @@
       </c>
       <c r="N93" s="66" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="O93" s="67" t="inlineStr">
         <is>
-          <t>sprint-3/be-nhanh, sprint-3/fe-khoi</t>
+          <t>sprint-3/be-nhanh (BE xong, chờ FE)</t>
         </is>
       </c>
     </row>
@@ -8785,12 +8783,12 @@
       </c>
       <c r="N94" s="66" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="O94" s="67" t="inlineStr">
         <is>
-          <t>sprint-3/be-nhanh, sprint-3/fe-khai</t>
+          <t>sprint-3/be-nhanh (BE xong, chờ FE)</t>
         </is>
       </c>
     </row>
@@ -8858,12 +8856,12 @@
       </c>
       <c r="N95" s="66" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="O95" s="67" t="inlineStr">
         <is>
-          <t>sprint-3/be-nhanh, sprint-3/fe-khai</t>
+          <t>sprint-3/be-nhanh (BE xong, chờ FE)</t>
         </is>
       </c>
     </row>
@@ -8931,12 +8929,12 @@
       </c>
       <c r="N96" s="66" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="O96" s="67" t="inlineStr">
         <is>
-          <t>sprint-3/be-nhanh, sprint-3/fe-khai</t>
+          <t>sprint-3/be-nhanh (BE xong, chờ FE)</t>
         </is>
       </c>
     </row>
@@ -9004,12 +9002,12 @@
       </c>
       <c r="N97" s="66" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="O97" s="67" t="inlineStr">
         <is>
-          <t>sprint-3/be-nhanh, sprint-3/fe-khoi</t>
+          <t>sprint-3/be-nhanh (BE xong, chờ FE)</t>
         </is>
       </c>
     </row>
@@ -9077,7 +9075,7 @@
       </c>
       <c r="N98" s="66" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="O98" s="67" t="inlineStr">
@@ -9150,12 +9148,12 @@
       </c>
       <c r="N99" s="66" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="O99" s="67" t="inlineStr">
         <is>
-          <t>sprint-3/be-nhanh, sprint-3/fe-khai</t>
+          <t>sprint-3/be-nhanh (BE xong, chờ FE)</t>
         </is>
       </c>
     </row>
@@ -9223,7 +9221,7 @@
       </c>
       <c r="N100" s="66" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="O100" s="67" t="inlineStr">
@@ -9661,7 +9659,7 @@
       </c>
       <c r="N106" s="62" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="O106" s="63" t="inlineStr">
